--- a/src/test/resources/Team03_RestAssured_Rebels_TestDataSheet.xlsx
+++ b/src/test/resources/Team03_RestAssured_Rebels_TestDataSheet.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maya/mayaIntellijProjects/Team01_RestAssured_Rebels/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFB70D7-4B42-714E-B842-39944A9E5D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F87580-61B9-3A42-B999-42280F8C2D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="Program" sheetId="2" r:id="rId2"/>
     <sheet name="Batch" sheetId="3" r:id="rId3"/>
+    <sheet name="User" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>ScenarioName</t>
   </si>
@@ -95,12 +96,47 @@
  "password": "Team01@sep26"
  }</t>
   </si>
+  <si>
+    <t>/users/roleStatus</t>
+  </si>
+  <si>
+    <t>ExpectedStatusMessage</t>
+  </si>
+  <si>
+    <t>CreateUser_with_valid_mandatory_feilds</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "teamonenwstaff",
+  "userLastName": "teamonstafflnwastname",
+  "userMiddleName": "teamonenwmiddilestaff",
+  "userPhoneNumber": "+2 5810979490",
+  "userLocation": "India",
+  "userTimeZone": "IST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "staff education",
+  "userEduPg": "staffedypg",
+  "userComments": "nothing",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "team01nwstaff@gmail.com",
+    "loginStatus": "active",
+    "status": "active"
+  }
+}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -183,6 +219,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -217,7 +266,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -255,6 +304,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4616,4 +4675,53 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134C0048-3788-6449-B1E6-05221D1E9B1B}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42.83203125" customWidth="1"/>
+    <col min="4" max="4" width="34.1640625" customWidth="1"/>
+    <col min="5" max="5" width="31.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="334">
+      <c r="A2" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="12">
+        <v>201</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>